--- a/docs/data/jp/xlsx/8260.xlsx
+++ b/docs/data/jp/xlsx/8260.xlsx
@@ -7207,7 +7207,7 @@
     <row r="99">
       <c r="A99" s="18" t="inlineStr">
         <is>
-          <t>System Installation Contribution Income NOI</t>
+          <t>시스템 도입 분담금 수입</t>
         </is>
       </c>
       <c r="C99" s="20" t="n">
@@ -11470,7 +11470,7 @@
     <row r="178">
       <c r="A178" s="18" t="inlineStr">
         <is>
-          <t>Increase Decrease In Provision For Point Vouchers Ope CF</t>
+          <t>포인트·상품권 충당금 증감</t>
         </is>
       </c>
       <c r="O178" s="20" t="n">
@@ -11572,7 +11572,7 @@
     <row r="181">
       <c r="A181" s="18" t="inlineStr">
         <is>
-          <t>Increase Decrease In Provision For Loss On PCBOpe CF</t>
+          <t>PCB 폐기물 처리비용 충당금 증감</t>
         </is>
       </c>
       <c r="O181" s="20" t="n">
@@ -11683,7 +11683,7 @@
     <row r="184">
       <c r="A184" s="18" t="inlineStr">
         <is>
-          <t>Increase Decrease In Provision For Employee Stock Ownership Plan Trust Ope CF</t>
+          <t>직원 주식급여 충당금 증감</t>
         </is>
       </c>
       <c r="D184" s="20" t="n">
@@ -12014,7 +12014,7 @@
     <row r="194">
       <c r="A194" s="18" t="inlineStr">
         <is>
-          <t>Loss On Valuation Of Membership Ope CF</t>
+          <t>회원권 평가손실</t>
         </is>
       </c>
       <c r="O194" s="20" t="n">
@@ -12776,7 +12776,7 @@
     <row r="212">
       <c r="A212" s="18" t="inlineStr">
         <is>
-          <t>Proceeds From Withdrawal Of Investment Securities Inv CF</t>
+          <t>투자유가증권 환급 수입</t>
         </is>
       </c>
       <c r="R212" s="20" t="n">
@@ -13043,7 +13043,7 @@
     <row r="221">
       <c r="A221" s="18" t="inlineStr">
         <is>
-          <t>Proceeds From Sales Of Membership Inv CF</t>
+          <t>회원권 매각 수입</t>
         </is>
       </c>
       <c r="R221" s="20" t="n">
@@ -13273,7 +13273,7 @@
     <row r="226">
       <c r="A226" s="18" t="inlineStr">
         <is>
-          <t>Decrease Increase In Other Net Inv CF</t>
+          <t>기타 증감</t>
         </is>
       </c>
       <c r="F226" s="20" t="n">
@@ -17682,7 +17682,7 @@
     <row r="109">
       <c r="A109" s="18" t="inlineStr">
         <is>
-          <t>Provision For Point Vouchers CL</t>
+          <t>포인트·상품권 충당금</t>
         </is>
       </c>
       <c r="H109" s="20" t="n">
@@ -17720,7 +17720,7 @@
     <row r="111">
       <c r="A111" s="18" t="inlineStr">
         <is>
-          <t>Electronically Recorded Obligations Facilities CL</t>
+          <t>설비 관련 전자기록채무</t>
         </is>
       </c>
       <c r="E111" s="20" t="n">
@@ -18061,7 +18061,7 @@
     <row r="122">
       <c r="A122" s="18" t="inlineStr">
         <is>
-          <t>Provision For Share Based Remuneration For Directors And Other Officers NCL</t>
+          <t>임원 주식급여 충당금</t>
         </is>
       </c>
       <c r="C122" s="20" t="n">
@@ -18105,7 +18105,7 @@
     <row r="124">
       <c r="A124" s="18" t="inlineStr">
         <is>
-          <t>Allowance For Employee Share Benefits Provisions</t>
+          <t>직원 주식급여 충당금</t>
         </is>
       </c>
       <c r="I124" s="20" t="n">
@@ -18121,7 +18121,7 @@
     <row r="125">
       <c r="A125" s="18" t="inlineStr">
         <is>
-          <t>Allowance For Employee Share Benefits NCL</t>
+          <t>직원 주식급여 충당금</t>
         </is>
       </c>
       <c r="C125" s="20" t="n">
